--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/92.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/92.xlsx
@@ -426,13 +426,13 @@
         <v>-2.507487906085227</v>
       </c>
       <c r="E2">
-        <v>-3.720831481763514</v>
+        <v>-4.491476455930749</v>
       </c>
       <c r="F2">
-        <v>-0.0116411943590492</v>
+        <v>-1.153558912996612</v>
       </c>
       <c r="G2">
-        <v>-10.82012598391629</v>
+        <v>-12.78571773076891</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.417030261857338</v>
       </c>
       <c r="E3">
-        <v>-4.482243867155654</v>
+        <v>-5.628592490978205</v>
       </c>
       <c r="F3">
-        <v>0.6443810568184081</v>
+        <v>-0.951259996089334</v>
       </c>
       <c r="G3">
-        <v>-11.35112141018593</v>
+        <v>-12.45915796507868</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.30171589148729</v>
       </c>
       <c r="E4">
-        <v>-4.755151383310138</v>
+        <v>-6.449570233191037</v>
       </c>
       <c r="F4">
-        <v>0.8132719163707824</v>
+        <v>-0.6740882631126195</v>
       </c>
       <c r="G4">
-        <v>-10.48483588831338</v>
+        <v>-11.79267664288092</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.170913075211235</v>
       </c>
       <c r="E5">
-        <v>-5.582271725072392</v>
+        <v>-7.223978016818567</v>
       </c>
       <c r="F5">
-        <v>1.061536940459405</v>
+        <v>-0.7489378848947772</v>
       </c>
       <c r="G5">
-        <v>-10.52965845682591</v>
+        <v>-11.87110079965337</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.018515641559241</v>
       </c>
       <c r="E6">
-        <v>-6.713706167027483</v>
+        <v>-7.407848988591376</v>
       </c>
       <c r="F6">
-        <v>1.162917513418426</v>
+        <v>-0.4027482366516134</v>
       </c>
       <c r="G6">
-        <v>-9.823783609492835</v>
+        <v>-11.46732565193638</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.84096495869091</v>
       </c>
       <c r="E7">
-        <v>-6.568551431224725</v>
+        <v>-9.07525535201559</v>
       </c>
       <c r="F7">
-        <v>0.6726631766847888</v>
+        <v>-0.2068136665000435</v>
       </c>
       <c r="G7">
-        <v>-8.874054774371418</v>
+        <v>-11.20272016076557</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.634783780040012</v>
       </c>
       <c r="E8">
-        <v>-8.222347721137476</v>
+        <v>-9.572195393453974</v>
       </c>
       <c r="F8">
-        <v>1.087512885476392</v>
+        <v>0.1350328514502425</v>
       </c>
       <c r="G8">
-        <v>-8.669150485137893</v>
+        <v>-10.80686731751032</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.400104338109509</v>
       </c>
       <c r="E9">
-        <v>-9.044733401989426</v>
+        <v>-10.74428977427914</v>
       </c>
       <c r="F9">
-        <v>1.108049770126598</v>
+        <v>0.1003234289055404</v>
       </c>
       <c r="G9">
-        <v>-8.630608062739286</v>
+        <v>-9.859351088429868</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.140030577107696</v>
       </c>
       <c r="E10">
-        <v>-9.15880965744849</v>
+        <v>-11.40364529778627</v>
       </c>
       <c r="F10">
-        <v>1.552309835187195</v>
+        <v>0.309645244653753</v>
       </c>
       <c r="G10">
-        <v>-9.079601306774357</v>
+        <v>-9.207093102764489</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.8670586165047802</v>
       </c>
       <c r="E11">
-        <v>-11.32767890944383</v>
+        <v>-11.94174781666503</v>
       </c>
       <c r="F11">
-        <v>1.395403795218524</v>
+        <v>0.6856552910302962</v>
       </c>
       <c r="G11">
-        <v>-7.937301339867833</v>
+        <v>-8.86475008064869</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.5971889896808761</v>
       </c>
       <c r="E12">
-        <v>-11.74249750335638</v>
+        <v>-13.11182373678632</v>
       </c>
       <c r="F12">
-        <v>1.691203854349394</v>
+        <v>0.476893451646376</v>
       </c>
       <c r="G12">
-        <v>-7.211872015547322</v>
+        <v>-8.393257439727405</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.3460061993711637</v>
       </c>
       <c r="E13">
-        <v>-12.25891610590821</v>
+        <v>-13.41257853487378</v>
       </c>
       <c r="F13">
-        <v>2.21349778548851</v>
+        <v>1.100962258628245</v>
       </c>
       <c r="G13">
-        <v>-6.525575141903008</v>
+        <v>-7.834430170744197</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.1286890631967849</v>
       </c>
       <c r="E14">
-        <v>-13.74673761164684</v>
+        <v>-14.28550049112624</v>
       </c>
       <c r="F14">
-        <v>2.441207700844066</v>
+        <v>1.065884212589297</v>
       </c>
       <c r="G14">
-        <v>-5.879924950797737</v>
+        <v>-7.203998009860525</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.04480991021961892</v>
       </c>
       <c r="E15">
-        <v>-14.55908082751535</v>
+        <v>-14.97851363920978</v>
       </c>
       <c r="F15">
-        <v>2.09624237962224</v>
+        <v>0.9490496173636495</v>
       </c>
       <c r="G15">
-        <v>-5.684012065936005</v>
+        <v>-6.736732164432251</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.1714621766831707</v>
       </c>
       <c r="E16">
-        <v>-15.05092072544685</v>
+        <v>-16.52155208951201</v>
       </c>
       <c r="F16">
-        <v>2.481638657039904</v>
+        <v>1.306564704737888</v>
       </c>
       <c r="G16">
-        <v>-4.992652958529523</v>
+        <v>-6.34125657377041</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.252569691347526</v>
       </c>
       <c r="E17">
-        <v>-15.22753603703518</v>
+        <v>-16.73204514587697</v>
       </c>
       <c r="F17">
-        <v>2.724030556242679</v>
+        <v>1.735296194465606</v>
       </c>
       <c r="G17">
-        <v>-4.663780073131574</v>
+        <v>-5.361117785651706</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.2949875114570148</v>
       </c>
       <c r="E18">
-        <v>-16.26596346458206</v>
+        <v>-17.07420746087297</v>
       </c>
       <c r="F18">
-        <v>2.941737106842028</v>
+        <v>1.786499240367449</v>
       </c>
       <c r="G18">
-        <v>-4.273847093236666</v>
+        <v>-5.22206430723983</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.308012774516048</v>
       </c>
       <c r="E19">
-        <v>-17.5619730584948</v>
+        <v>-17.95730063165993</v>
       </c>
       <c r="F19">
-        <v>2.982184630385922</v>
+        <v>1.952646547081751</v>
       </c>
       <c r="G19">
-        <v>-3.209347315145318</v>
+        <v>-4.800906822035207</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.2980717833001086</v>
       </c>
       <c r="E20">
-        <v>-17.19585917378852</v>
+        <v>-18.58050660379576</v>
       </c>
       <c r="F20">
-        <v>3.565539179520196</v>
+        <v>2.150818537588282</v>
       </c>
       <c r="G20">
-        <v>-3.477353301146052</v>
+        <v>-4.75790263713039</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.2678091286246438</v>
       </c>
       <c r="E21">
-        <v>-18.4650597885995</v>
+        <v>-19.96832293404384</v>
       </c>
       <c r="F21">
-        <v>3.564546795371642</v>
+        <v>2.309624852378976</v>
       </c>
       <c r="G21">
-        <v>-3.770046488000353</v>
+        <v>-4.240280750028723</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.2163813243470372</v>
       </c>
       <c r="E22">
-        <v>-17.99239942056606</v>
+        <v>-19.89360250909885</v>
       </c>
       <c r="F22">
-        <v>3.796981718392766</v>
+        <v>2.480904723521024</v>
       </c>
       <c r="G22">
-        <v>-3.472019549946407</v>
+        <v>-4.225464774474155</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.1408285323359584</v>
       </c>
       <c r="E23">
-        <v>-20.1945732741752</v>
+        <v>-20.34747374909876</v>
       </c>
       <c r="F23">
-        <v>3.900648585383514</v>
+        <v>2.676651254272159</v>
       </c>
       <c r="G23">
-        <v>-3.461195402871652</v>
+        <v>-4.012947554012943</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.03898068870894025</v>
       </c>
       <c r="E24">
-        <v>-20.57830092811008</v>
+        <v>-20.59239277413522</v>
       </c>
       <c r="F24">
-        <v>4.369885584373321</v>
+        <v>2.877106225340805</v>
       </c>
       <c r="G24">
-        <v>-2.412769979227787</v>
+        <v>-3.601334951033431</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.08864870242949886</v>
       </c>
       <c r="E25">
-        <v>-20.08317168680932</v>
+        <v>-21.74365880016637</v>
       </c>
       <c r="F25">
-        <v>4.241906134110409</v>
+        <v>2.754854107300849</v>
       </c>
       <c r="G25">
-        <v>-2.510691176606673</v>
+        <v>-4.260461805718029</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.2363948741685386</v>
       </c>
       <c r="E26">
-        <v>-19.40948758423153</v>
+        <v>-21.19262733443342</v>
       </c>
       <c r="F26">
-        <v>4.132387679786286</v>
+        <v>3.148688135083429</v>
       </c>
       <c r="G26">
-        <v>-3.403014959658692</v>
+        <v>-4.463768319261793</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.3928006111927309</v>
       </c>
       <c r="E27">
-        <v>-19.54828375349598</v>
+        <v>-21.11416901929609</v>
       </c>
       <c r="F27">
-        <v>3.941566621612198</v>
+        <v>3.314585274842086</v>
       </c>
       <c r="G27">
-        <v>-3.167512743817318</v>
+        <v>-4.386947159668285</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.5436169244500342</v>
       </c>
       <c r="E28">
-        <v>-20.11997744556995</v>
+        <v>-20.59954875724791</v>
       </c>
       <c r="F28">
-        <v>4.488829203006497</v>
+        <v>3.281858135492283</v>
       </c>
       <c r="G28">
-        <v>-3.024169812042243</v>
+        <v>-4.258258337283129</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.674856229216441</v>
       </c>
       <c r="E29">
-        <v>-19.47376268269458</v>
+        <v>-20.73560796024929</v>
       </c>
       <c r="F29">
-        <v>4.509458864805816</v>
+        <v>2.896582799715427</v>
       </c>
       <c r="G29">
-        <v>-3.057911075137791</v>
+        <v>-4.4579202513777</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7754811133644999</v>
       </c>
       <c r="E30">
-        <v>-19.23416807457655</v>
+        <v>-21.21426141222445</v>
       </c>
       <c r="F30">
-        <v>3.814799901226984</v>
+        <v>3.190853692620729</v>
       </c>
       <c r="G30">
-        <v>-3.304177390928325</v>
+        <v>-4.845315587530044</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.8395181679066221</v>
       </c>
       <c r="E31">
-        <v>-18.63815317698438</v>
+        <v>-20.11405911943207</v>
       </c>
       <c r="F31">
-        <v>4.564765642821127</v>
+        <v>3.286241855787898</v>
       </c>
       <c r="G31">
-        <v>-3.67611711910128</v>
+        <v>-5.026370724923751</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.8640767915959581</v>
       </c>
       <c r="E32">
-        <v>-18.97035609122344</v>
+        <v>-20.03236129946137</v>
       </c>
       <c r="F32">
-        <v>4.171431948949838</v>
+        <v>3.332305710322772</v>
       </c>
       <c r="G32">
-        <v>-4.275632842536988</v>
+        <v>-5.068239235931435</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.8494717918165042</v>
       </c>
       <c r="E33">
-        <v>-18.36997201531755</v>
+        <v>-19.68519021160763</v>
       </c>
       <c r="F33">
-        <v>4.422013088296689</v>
+        <v>3.316205561481961</v>
       </c>
       <c r="G33">
-        <v>-3.906363906080742</v>
+        <v>-5.498382904018668</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.8004447281747419</v>
       </c>
       <c r="E34">
-        <v>-17.91988435083455</v>
+        <v>-19.12550760668506</v>
       </c>
       <c r="F34">
-        <v>4.233347442104685</v>
+        <v>3.234410907394733</v>
       </c>
       <c r="G34">
-        <v>-4.680919611372232</v>
+        <v>-5.565392885438773</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.7242590732994438</v>
       </c>
       <c r="E35">
-        <v>-17.78520401399301</v>
+        <v>-18.22720537602657</v>
       </c>
       <c r="F35">
-        <v>3.629298618513674</v>
+        <v>3.136776211831172</v>
       </c>
       <c r="G35">
-        <v>-4.186896244629638</v>
+        <v>-5.879186110078452</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6298329448120319</v>
       </c>
       <c r="E36">
-        <v>-17.67566306530066</v>
+        <v>-17.21583612026095</v>
       </c>
       <c r="F36">
-        <v>4.26935988657399</v>
+        <v>3.206269609986828</v>
       </c>
       <c r="G36">
-        <v>-4.394834219078038</v>
+        <v>-6.104409824464613</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5281556700957821</v>
       </c>
       <c r="E37">
-        <v>-15.81793163970486</v>
+        <v>-17.07659140417342</v>
       </c>
       <c r="F37">
-        <v>4.155439487871391</v>
+        <v>3.244985845658871</v>
       </c>
       <c r="G37">
-        <v>-4.426975095739234</v>
+        <v>-5.830007514215652</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.4307422925025495</v>
       </c>
       <c r="E38">
-        <v>-16.0579457221667</v>
+        <v>-16.58486364294769</v>
       </c>
       <c r="F38">
-        <v>3.804877716476252</v>
+        <v>3.219998971320827</v>
       </c>
       <c r="G38">
-        <v>-4.912811167444096</v>
+        <v>-6.437713143433682</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.3472184871070565</v>
       </c>
       <c r="E39">
-        <v>-16.147974884055</v>
+        <v>-16.1383062080908</v>
       </c>
       <c r="F39">
-        <v>4.432428980019489</v>
+        <v>3.106683280822272</v>
       </c>
       <c r="G39">
-        <v>-4.876576643264035</v>
+        <v>-6.561044717917873</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.2842333362092143</v>
       </c>
       <c r="E40">
-        <v>-15.24456420346698</v>
+        <v>-15.51196040819341</v>
       </c>
       <c r="F40">
-        <v>4.178259353083712</v>
+        <v>2.855161116105841</v>
       </c>
       <c r="G40">
-        <v>-5.314304524388453</v>
+        <v>-6.88519737709509</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.2450755592391079</v>
       </c>
       <c r="E41">
-        <v>-14.76665417631895</v>
+        <v>-14.50086526437523</v>
       </c>
       <c r="F41">
-        <v>3.921859761099598</v>
+        <v>3.241210147036911</v>
       </c>
       <c r="G41">
-        <v>-4.480174238272349</v>
+        <v>-7.450235607460557</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.2307419366316854</v>
       </c>
       <c r="E42">
-        <v>-14.11542648737452</v>
+        <v>-14.81668791314917</v>
       </c>
       <c r="F42">
-        <v>4.308114227146563</v>
+        <v>3.042966916933739</v>
       </c>
       <c r="G42">
-        <v>-5.320839218100009</v>
+        <v>-7.096764286525137</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.2389550775446117</v>
       </c>
       <c r="E43">
-        <v>-13.72193048040364</v>
+        <v>-13.11631335822846</v>
       </c>
       <c r="F43">
-        <v>4.197762435215223</v>
+        <v>3.102998702614619</v>
       </c>
       <c r="G43">
-        <v>-5.559542206810089</v>
+        <v>-7.576102214942719</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.2641202810362602</v>
       </c>
       <c r="E44">
-        <v>-13.22810119424755</v>
+        <v>-13.63256998553862</v>
       </c>
       <c r="F44">
-        <v>3.832031599940019</v>
+        <v>3.121012380155897</v>
       </c>
       <c r="G44">
-        <v>-5.34785520312885</v>
+        <v>-7.674272738430057</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.3001563725013072</v>
       </c>
       <c r="E45">
-        <v>-11.41047317720428</v>
+        <v>-12.13348497068706</v>
       </c>
       <c r="F45">
-        <v>4.110068148485256</v>
+        <v>2.934478951658699</v>
       </c>
       <c r="G45">
-        <v>-5.176444156254716</v>
+        <v>-7.439863119200063</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.341930685482179</v>
       </c>
       <c r="E46">
-        <v>-11.42407079108177</v>
+        <v>-11.97351988329996</v>
       </c>
       <c r="F46">
-        <v>4.204442389951399</v>
+        <v>2.802836460740607</v>
       </c>
       <c r="G46">
-        <v>-6.001256694925137</v>
+        <v>-7.863563469636429</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.3851903559712148</v>
       </c>
       <c r="E47">
-        <v>-12.29574678393679</v>
+        <v>-10.98472333108479</v>
       </c>
       <c r="F47">
-        <v>4.126362135298323</v>
+        <v>2.949356430212978</v>
       </c>
       <c r="G47">
-        <v>-5.73934157605547</v>
+        <v>-7.979062810347282</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.4263203202662486</v>
       </c>
       <c r="E48">
-        <v>-10.33802679569573</v>
+        <v>-10.2341092951372</v>
       </c>
       <c r="F48">
-        <v>4.075634572285686</v>
+        <v>2.618032663380454</v>
       </c>
       <c r="G48">
-        <v>-5.871069305144681</v>
+        <v>-8.153433136215442</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.4633246792116335</v>
       </c>
       <c r="E49">
-        <v>-9.676598819737515</v>
+        <v>-9.909677039286892</v>
       </c>
       <c r="F49">
-        <v>3.797097689829159</v>
+        <v>2.941637702753692</v>
       </c>
       <c r="G49">
-        <v>-5.890091190235532</v>
+        <v>-8.112967900425481</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.4957290552683354</v>
       </c>
       <c r="E50">
-        <v>-9.616692899588188</v>
+        <v>-9.002320807940276</v>
       </c>
       <c r="F50">
-        <v>3.643768540305776</v>
+        <v>2.835197461698372</v>
       </c>
       <c r="G50">
-        <v>-5.832988984538702</v>
+        <v>-8.337450163347766</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.5243943759102818</v>
       </c>
       <c r="E51">
-        <v>-8.340896985193382</v>
+        <v>-8.213032068135885</v>
       </c>
       <c r="F51">
-        <v>3.833777798425121</v>
+        <v>2.7663501901169</v>
       </c>
       <c r="G51">
-        <v>-6.029105507478541</v>
+        <v>-8.196558720743747</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.5524640807120282</v>
       </c>
       <c r="E52">
-        <v>-7.988891559357539</v>
+        <v>-7.860270757838924</v>
       </c>
       <c r="F52">
-        <v>3.375183663826481</v>
+        <v>2.626737148049072</v>
       </c>
       <c r="G52">
-        <v>-5.967387505344623</v>
+        <v>-8.682525329678166</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.5842446205181671</v>
       </c>
       <c r="E53">
-        <v>-8.459064153807404</v>
+        <v>-7.095618867613416</v>
       </c>
       <c r="F53">
-        <v>3.052073988160117</v>
+        <v>2.421338480320517</v>
       </c>
       <c r="G53">
-        <v>-6.964177622465449</v>
+        <v>-8.445302633151247</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.6246324073584202</v>
       </c>
       <c r="E54">
-        <v>-8.632539637634167</v>
+        <v>-6.75435364626358</v>
       </c>
       <c r="F54">
-        <v>3.167950990668128</v>
+        <v>2.675247999891816</v>
       </c>
       <c r="G54">
-        <v>-6.327811239126177</v>
+        <v>-8.898935170324728</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.6798875617709277</v>
       </c>
       <c r="E55">
-        <v>-7.380471019538106</v>
+        <v>-6.678383104709816</v>
       </c>
       <c r="F55">
-        <v>3.62541523212935</v>
+        <v>2.416547203262725</v>
       </c>
       <c r="G55">
-        <v>-6.686960929547268</v>
+        <v>-8.933206414572272</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.7547006682042103</v>
       </c>
       <c r="E56">
-        <v>-6.917936180714602</v>
+        <v>-5.698262610952203</v>
       </c>
       <c r="F56">
-        <v>3.410344546605709</v>
+        <v>2.172448867210183</v>
       </c>
       <c r="G56">
-        <v>-6.099480738676592</v>
+        <v>-8.98366688602931</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.8515700555997211</v>
       </c>
       <c r="E57">
-        <v>-6.583606822277228</v>
+        <v>-5.229348439533762</v>
       </c>
       <c r="F57">
-        <v>3.424698496961418</v>
+        <v>2.194733607080296</v>
       </c>
       <c r="G57">
-        <v>-7.096216030161004</v>
+        <v>-8.981133158403633</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.9732022793899675</v>
       </c>
       <c r="E58">
-        <v>-6.489490900445289</v>
+        <v>-5.44426051274834</v>
       </c>
       <c r="F58">
-        <v>3.032617294603162</v>
+        <v>2.108752384139318</v>
       </c>
       <c r="G58">
-        <v>-7.238697416221012</v>
+        <v>-9.49475669016401</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.12073862806472</v>
       </c>
       <c r="E59">
-        <v>-5.815055066617707</v>
+        <v>-4.623723010935939</v>
       </c>
       <c r="F59">
-        <v>3.068800382757444</v>
+        <v>2.00268822188487</v>
       </c>
       <c r="G59">
-        <v>-7.102695898236147</v>
+        <v>-9.454869734300981</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.293437564481775</v>
       </c>
       <c r="E60">
-        <v>-5.347947542125565</v>
+        <v>-4.408690494592941</v>
       </c>
       <c r="F60">
-        <v>3.129125410498915</v>
+        <v>2.146680014043896</v>
       </c>
       <c r="G60">
-        <v>-7.307889980119286</v>
+        <v>-9.347368409645005</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.491549691209318</v>
       </c>
       <c r="E61">
-        <v>-4.214785364259346</v>
+        <v>-3.587849808353828</v>
       </c>
       <c r="F61">
-        <v>2.895563907809984</v>
+        <v>1.811665042064498</v>
       </c>
       <c r="G61">
-        <v>-7.04787548331195</v>
+        <v>-9.817836333314279</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.713322710790542</v>
       </c>
       <c r="E62">
-        <v>-5.01841514276837</v>
+        <v>-3.427436174143651</v>
       </c>
       <c r="F62">
-        <v>3.118951402057732</v>
+        <v>1.900398101517575</v>
       </c>
       <c r="G62">
-        <v>-6.525384557547858</v>
+        <v>-9.695802298891872</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.954613341474714</v>
       </c>
       <c r="E63">
-        <v>-3.845108024236358</v>
+        <v>-3.241837466459713</v>
       </c>
       <c r="F63">
-        <v>3.188777803909313</v>
+        <v>1.83360352436024</v>
       </c>
       <c r="G63">
-        <v>-7.052055285402322</v>
+        <v>-9.518423089882452</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.212504246371284</v>
       </c>
       <c r="E64">
-        <v>-4.473854380279501</v>
+        <v>-3.52191342536085</v>
       </c>
       <c r="F64">
-        <v>2.886417074948271</v>
+        <v>1.496207824465196</v>
       </c>
       <c r="G64">
-        <v>-6.934887678897749</v>
+        <v>-9.473296369625059</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.482337432998388</v>
       </c>
       <c r="E65">
-        <v>-3.614907980135086</v>
+        <v>-2.032534465375412</v>
       </c>
       <c r="F65">
-        <v>3.117501759102833</v>
+        <v>1.612046722072679</v>
       </c>
       <c r="G65">
-        <v>-6.917455737262886</v>
+        <v>-9.889911159241144</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.757060101100884</v>
       </c>
       <c r="E66">
-        <v>-3.947243797136541</v>
+        <v>-3.537201396247544</v>
       </c>
       <c r="F66">
-        <v>2.839567928115543</v>
+        <v>1.786679824461259</v>
       </c>
       <c r="G66">
-        <v>-7.10143751934323</v>
+        <v>-9.505956784459887</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.029803233155478</v>
       </c>
       <c r="E67">
-        <v>-4.787986672044233</v>
+        <v>-2.593571017189876</v>
       </c>
       <c r="F67">
-        <v>3.267141360214147</v>
+        <v>1.30889407387456</v>
       </c>
       <c r="G67">
-        <v>-7.436437822296523</v>
+        <v>-9.27040235372669</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.291659955487351</v>
       </c>
       <c r="E68">
-        <v>-4.898956325432327</v>
+        <v>-3.009170414831493</v>
       </c>
       <c r="F68">
-        <v>2.567590058754381</v>
+        <v>1.488260467602737</v>
       </c>
       <c r="G68">
-        <v>-6.717506641263292</v>
+        <v>-9.296930129516992</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.532120162512193</v>
       </c>
       <c r="E69">
-        <v>-3.471231787563968</v>
+        <v>-2.85846283548744</v>
       </c>
       <c r="F69">
-        <v>2.652409910596634</v>
+        <v>1.615022217783534</v>
       </c>
       <c r="G69">
-        <v>-6.900407575082916</v>
+        <v>-9.215823432677171</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.741823147744976</v>
       </c>
       <c r="E70">
-        <v>-3.580365721546487</v>
+        <v>-2.533283001598664</v>
       </c>
       <c r="F70">
-        <v>2.866299344203883</v>
+        <v>1.193055176267077</v>
       </c>
       <c r="G70">
-        <v>-6.484975452766606</v>
+        <v>-8.850576348263536</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.910644432095429</v>
       </c>
       <c r="E71">
-        <v>-3.824483176797259</v>
+        <v>-2.835387593366693</v>
       </c>
       <c r="F71">
-        <v>3.26626660423679</v>
+        <v>1.379161167184431</v>
       </c>
       <c r="G71">
-        <v>-6.477017903252893</v>
+        <v>-8.93999043439228</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.028626475742643</v>
       </c>
       <c r="E72">
-        <v>-3.972561773372696</v>
+        <v>-2.993354986106546</v>
       </c>
       <c r="F72">
-        <v>2.916450363504171</v>
+        <v>1.388581361289067</v>
       </c>
       <c r="G72">
-        <v>-6.82314519965351</v>
+        <v>-8.453039574747011</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.089016862540544</v>
       </c>
       <c r="E73">
-        <v>-5.364506395677657</v>
+        <v>-3.824088621721401</v>
       </c>
       <c r="F73">
-        <v>2.593272761710777</v>
+        <v>1.458951172156885</v>
       </c>
       <c r="G73">
-        <v>-7.368159019005137</v>
+        <v>-8.406258947791148</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.087637205675475</v>
       </c>
       <c r="E74">
-        <v>-4.783538582715341</v>
+        <v>-3.496421014249053</v>
       </c>
       <c r="F74">
-        <v>2.4797731736488</v>
+        <v>1.371235347874445</v>
       </c>
       <c r="G74">
-        <v>-6.110957571899125</v>
+        <v>-8.360033104060896</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.024445438592639</v>
       </c>
       <c r="E75">
-        <v>-5.594706439778928</v>
+        <v>-4.119402712973334</v>
       </c>
       <c r="F75">
-        <v>2.415983913428821</v>
+        <v>1.425611040929011</v>
       </c>
       <c r="G75">
-        <v>-6.418145612723288</v>
+        <v>-7.778125547519952</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.904608647934386</v>
       </c>
       <c r="E76">
-        <v>-5.065184455497264</v>
+        <v>-4.584363027210539</v>
       </c>
       <c r="F76">
-        <v>2.658253214255981</v>
+        <v>1.381208891404152</v>
       </c>
       <c r="G76">
-        <v>-5.85111016274562</v>
+        <v>-8.108866420672843</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.735700988802352</v>
       </c>
       <c r="E77">
-        <v>-6.399320529371937</v>
+        <v>-5.436352798385866</v>
       </c>
       <c r="F77">
-        <v>2.749164879978422</v>
+        <v>1.21506489815946</v>
       </c>
       <c r="G77">
-        <v>-5.058582091688907</v>
+        <v>-7.219174268168667</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.526507501980954</v>
       </c>
       <c r="E78">
-        <v>-6.835075461572947</v>
+        <v>-5.933201469175104</v>
       </c>
       <c r="F78">
-        <v>2.664941452666185</v>
+        <v>1.42163984759999</v>
       </c>
       <c r="G78">
-        <v>-5.095787812856862</v>
+        <v>-7.502766399378347</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.285602202789996</v>
       </c>
       <c r="E79">
-        <v>-6.5188997898364</v>
+        <v>-6.063711981846517</v>
       </c>
       <c r="F79">
-        <v>2.458540460380243</v>
+        <v>1.40050985188938</v>
       </c>
       <c r="G79">
-        <v>-5.238953213999741</v>
+        <v>-6.455006715605216</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.019774648359039</v>
       </c>
       <c r="E80">
-        <v>-7.962855077562189</v>
+        <v>-6.432151664894706</v>
       </c>
       <c r="F80">
-        <v>2.516453282244762</v>
+        <v>1.424520909426926</v>
       </c>
       <c r="G80">
-        <v>-5.181811847134044</v>
+        <v>-6.155358505160189</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.73647932324513</v>
       </c>
       <c r="E81">
-        <v>-8.713822136472386</v>
+        <v>-8.002306431936734</v>
       </c>
       <c r="F81">
-        <v>2.284959384593218</v>
+        <v>1.53920009267049</v>
       </c>
       <c r="G81">
-        <v>-4.686457000649983</v>
+        <v>-6.324521700941374</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.443982922681353</v>
       </c>
       <c r="E82">
-        <v>-10.67938338769472</v>
+        <v>-8.504134803104442</v>
       </c>
       <c r="F82">
-        <v>2.333264801320068</v>
+        <v>1.576696971525613</v>
       </c>
       <c r="G82">
-        <v>-4.207980617947469</v>
+        <v>-5.850146797991499</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.148594396952232</v>
       </c>
       <c r="E83">
-        <v>-10.01791387962325</v>
+        <v>-9.96798397307616</v>
       </c>
       <c r="F83">
-        <v>2.081850324366001</v>
+        <v>1.581345769390123</v>
       </c>
       <c r="G83">
-        <v>-4.467405086477214</v>
+        <v>-5.265212083097158</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.856949909698975</v>
       </c>
       <c r="E84">
-        <v>-11.49178059531045</v>
+        <v>-10.63758546892164</v>
       </c>
       <c r="F84">
-        <v>2.51181608152389</v>
+        <v>1.511789415311854</v>
       </c>
       <c r="G84">
-        <v>-4.198125057116017</v>
+        <v>-5.013854815353953</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.576664622868373</v>
       </c>
       <c r="E85">
-        <v>-13.03023390031007</v>
+        <v>-12.21492944476695</v>
       </c>
       <c r="F85">
-        <v>2.749842484513911</v>
+        <v>1.789545975674945</v>
       </c>
       <c r="G85">
-        <v>-3.984299853614656</v>
+        <v>-4.898217105179773</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.313769867034957</v>
       </c>
       <c r="E86">
-        <v>-13.42763392592629</v>
+        <v>-13.84124393534331</v>
       </c>
       <c r="F86">
-        <v>2.112693756241838</v>
+        <v>1.695146883186719</v>
       </c>
       <c r="G86">
-        <v>-3.98062653597496</v>
+        <v>-4.591626924866976</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.0743236891039</v>
       </c>
       <c r="E87">
-        <v>-15.67893196308549</v>
+        <v>-14.92629946643404</v>
       </c>
       <c r="F87">
-        <v>2.56027226111805</v>
+        <v>1.529123831582837</v>
       </c>
       <c r="G87">
-        <v>-3.211156561146959</v>
+        <v>-4.025001361790112</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.8651101233877285</v>
       </c>
       <c r="E88">
-        <v>-16.70785268990984</v>
+        <v>-16.71379178210434</v>
       </c>
       <c r="F88">
-        <v>1.949985830983959</v>
+        <v>1.547970846731331</v>
       </c>
       <c r="G88">
-        <v>-2.657370639969191</v>
+        <v>-4.084993661749304</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.6916255398407527</v>
       </c>
       <c r="E89">
-        <v>-17.54871185473463</v>
+        <v>-18.08444288994691</v>
       </c>
       <c r="F89">
-        <v>2.210378153849567</v>
+        <v>1.737458233386912</v>
       </c>
       <c r="G89">
-        <v>-2.105942221157199</v>
+        <v>-3.500990982673991</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.559381508624869</v>
       </c>
       <c r="E90">
-        <v>-20.09639135845625</v>
+        <v>-19.15879559545356</v>
       </c>
       <c r="F90">
-        <v>2.478343411511568</v>
+        <v>1.745211752277116</v>
       </c>
       <c r="G90">
-        <v>-2.132498715138003</v>
+        <v>-3.424783348059395</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.4747469260529466</v>
       </c>
       <c r="E91">
-        <v>-21.46598339741098</v>
+        <v>-21.17389219814712</v>
       </c>
       <c r="F91">
-        <v>2.389699815737993</v>
+        <v>1.947028559355965</v>
       </c>
       <c r="G91">
-        <v>-2.185201816198806</v>
+        <v>-3.632267052948941</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4432787915336275</v>
       </c>
       <c r="E92">
-        <v>-23.44841499303477</v>
+        <v>-22.95157047545685</v>
       </c>
       <c r="F92">
-        <v>2.029139649791063</v>
+        <v>1.962189339562002</v>
       </c>
       <c r="G92">
-        <v>-2.523423777977533</v>
+        <v>-3.351591123447534</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.4672044393078454</v>
       </c>
       <c r="E93">
-        <v>-24.92719911093057</v>
+        <v>-25.22945321830629</v>
       </c>
       <c r="F93">
-        <v>2.10917319477994</v>
+        <v>1.816877129762912</v>
       </c>
       <c r="G93">
-        <v>-3.453689512172201</v>
+        <v>-3.199993017275359</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.545557626838936</v>
       </c>
       <c r="E94">
-        <v>-27.87859152148215</v>
+        <v>-27.50586987755806</v>
       </c>
       <c r="F94">
-        <v>2.238549272483973</v>
+        <v>2.041624803286057</v>
       </c>
       <c r="G94">
-        <v>-2.664706832270219</v>
+        <v>-3.184808926733444</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.6738623564314493</v>
       </c>
       <c r="E95">
-        <v>-30.74286617128413</v>
+        <v>-30.00518938861338</v>
       </c>
       <c r="F95">
-        <v>1.889082602795334</v>
+        <v>2.236132096402604</v>
       </c>
       <c r="G95">
-        <v>-2.545293985417289</v>
+        <v>-3.755648231580364</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.8446544054563383</v>
       </c>
       <c r="E96">
-        <v>-32.30292032838418</v>
+        <v>-32.20452867549332</v>
       </c>
       <c r="F96">
-        <v>1.566297647150867</v>
+        <v>2.254588122136977</v>
       </c>
       <c r="G96">
-        <v>-2.822886625556591</v>
+        <v>-3.442110859910613</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.046031574960338</v>
       </c>
       <c r="E97">
-        <v>-34.88466239478638</v>
+        <v>-34.07942740010031</v>
       </c>
       <c r="F97">
-        <v>1.880381431596328</v>
+        <v>2.285862305062269</v>
       </c>
       <c r="G97">
-        <v>-2.94025525939468</v>
+        <v>-3.807429739800504</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.268054565129465</v>
       </c>
       <c r="E98">
-        <v>-37.95365090739482</v>
+        <v>-37.01037770451109</v>
       </c>
       <c r="F98">
-        <v>2.017400026958589</v>
+        <v>2.365178483880322</v>
       </c>
       <c r="G98">
-        <v>-3.504771340841923</v>
+        <v>-4.053424538153562</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.490960579729509</v>
       </c>
       <c r="E99">
-        <v>-39.75252717530648</v>
+        <v>-39.33536617020673</v>
       </c>
       <c r="F99">
-        <v>1.687504365528491</v>
+        <v>2.261682260574552</v>
       </c>
       <c r="G99">
-        <v>-3.418232989880291</v>
+        <v>-4.289730863329</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.704010297260175</v>
       </c>
       <c r="E100">
-        <v>-42.92876198735031</v>
+        <v>-41.44989688183367</v>
       </c>
       <c r="F100">
-        <v>1.557970898017927</v>
+        <v>2.300206315009146</v>
       </c>
       <c r="G100">
-        <v>-3.386076448751549</v>
+        <v>-3.939086978785757</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.883945836395722</v>
       </c>
       <c r="E101">
-        <v>-45.5133417353902</v>
+        <v>-43.80369409788398</v>
       </c>
       <c r="F101">
-        <v>1.155929406008409</v>
+        <v>2.348511731735996</v>
       </c>
       <c r="G101">
-        <v>-3.182427927666348</v>
+        <v>-4.461348159025832</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.036128883254058</v>
       </c>
       <c r="E102">
-        <v>-47.85443323969503</v>
+        <v>-46.24073724342633</v>
       </c>
       <c r="F102">
-        <v>1.060536272636824</v>
+        <v>2.460722380119217</v>
       </c>
       <c r="G102">
-        <v>-4.07116976913936</v>
+        <v>-4.709567311770519</v>
       </c>
     </row>
   </sheetData>
